--- a/数据表/UIForm.xlsx
+++ b/数据表/UIForm.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>#</t>
   </si>
@@ -126,6 +126,21 @@
   </si>
   <si>
     <t>HudForm</t>
+  </si>
+  <si>
+    <t>HUD</t>
+  </si>
+  <si>
+    <t>角色升级奖励页</t>
+  </si>
+  <si>
+    <t>LevelUpForm</t>
+  </si>
+  <si>
+    <t>物品信息展示</t>
+  </si>
+  <si>
+    <t>DisplayItemInfoForm</t>
   </si>
 </sst>
 </file>
@@ -1273,13 +1288,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8.72727272727273" style="1"/>
     <col min="2" max="2" width="11.4545454545455" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.1818181818182" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.4545454545455" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.4545454545455" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.5454545454545" style="1" customWidth="1"/>
     <col min="6" max="6" width="24" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.1818181818182" style="1" customWidth="1"/>
@@ -1507,13 +1522,53 @@
         <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="1">
+        <v>204</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="1">
+        <v>205</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
